--- a/basedatos_partidas/salida/descompuestos/09.16.01.110.xlsx
+++ b/basedatos_partidas/salida/descompuestos/09.16.01.110.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -534,86 +534,86 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>Materiales</t>
+          <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-CONS-DEM</t>
+          <t>MQ-GRUA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ud</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Consumibles de demolición: puntas y cinceles de martillo, discos de corte y hojas de espátula.</t>
+          <t>Camión grúa o grúa móvil con operador, para izado y montaje de elementos estructurales.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>48</v>
       </c>
       <c r="H10" t="n">
-        <v>0.66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal materiales:</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MQ-TALADRO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.66</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal equipo y maquinaria:</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>Equipo y maquinaria</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MQ-GRUA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Camión grúa o grúa móvil con operador, para izado y montaje de elementos estructurales.</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>48</v>
-      </c>
-      <c r="H13" t="n">
-        <v>48</v>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Mano de obra</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MQ-TALADRO</t>
+          <t>MO-OF1-MON</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -623,146 +623,100 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Taladro percutor con brocas, incluida amortización y consumo.</t>
+          <t>Oficial de 1ª montador de prefabricados interiores.</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MO-AYU</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Ayudante.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal mano de obra:</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Costes directos complementarios</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal equipo y maquinaria:</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>Mano de obra</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MO-OF1-MON</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Oficial de 1ª montador de prefabricados interiores.</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MO-AYU</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Ayudante.</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
-      </c>
       <c r="G18" t="n">
-        <v>3.5</v>
+        <v>122</v>
       </c>
       <c r="H18" t="n">
-        <v>17.5</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="19">
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal mano de obra:</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Costes directos complementarios</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>122.66</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Costes directos (1+2+3+4):</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="5" t="n">
-        <v>123.89</v>
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Costes directos (1+2+3):</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="5" t="n">
+        <v>123.22</v>
       </c>
     </row>
   </sheetData>
